--- a/outputs/tables/portfolio_performance_metrics_all_methods_with_costs_taxes.xlsx
+++ b/outputs/tables/portfolio_performance_metrics_all_methods_with_costs_taxes.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,37 +417,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_return</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>annual_return</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>annual_volatility</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>sharpe_ratio</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>max_drawdown</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>n_days</t>
         </is>
@@ -472,16 +460,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.347727997906055</v>
+        <v>1.347727997906049</v>
       </c>
       <c r="C2" t="n">
-        <v>0.128581056096571</v>
+        <v>0.1285810560965706</v>
       </c>
       <c r="D2" t="n">
         <v>0.2007062047695774</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6406431542272928</v>
+        <v>0.6406431542272906</v>
       </c>
       <c r="F2" t="n">
         <v>-0.3971874807454868</v>
@@ -497,19 +485,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.233978572424518</v>
+        <v>1.233978572424533</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1206648857793291</v>
+        <v>0.12066488577933</v>
       </c>
       <c r="D3" t="n">
         <v>0.2030569221477386</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5942416761913523</v>
+        <v>0.5942416761913565</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4009292993887903</v>
+        <v>-0.4009292993887905</v>
       </c>
       <c r="G3" t="n">
         <v>1778</v>
@@ -522,19 +510,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.133313922826277</v>
+        <v>1.133313922826268</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1133653051047947</v>
+        <v>0.113365305104794</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2022388209588297</v>
+        <v>0.2022388209588296</v>
       </c>
       <c r="E4" t="n">
-        <v>0.560551651593503</v>
+        <v>0.5605516515934997</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.406205495133194</v>
+        <v>-0.4062054951331937</v>
       </c>
       <c r="G4" t="n">
         <v>1778</v>
@@ -547,16 +535,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.142132717376075</v>
+        <v>1.142132717376083</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1140164712067637</v>
+        <v>0.1140164712067644</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2043801037707084</v>
+        <v>0.2043801037707083</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5578648268751124</v>
+        <v>0.5578648268751157</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3964535505565089</v>
@@ -572,19 +560,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.078952148705082</v>
+        <v>1.078952148705079</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1092995219200823</v>
+        <v>0.1092995219200821</v>
       </c>
       <c r="D6" t="n">
         <v>0.1978310427979943</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5524892371501486</v>
+        <v>0.5524892371501475</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3886982348420295</v>
+        <v>-0.3886982348420296</v>
       </c>
       <c r="G6" t="n">
         <v>1778</v>
@@ -597,19 +585,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.052517221185633</v>
+        <v>1.052517221185644</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1072893494217741</v>
+        <v>0.1072893494217748</v>
       </c>
       <c r="D7" t="n">
         <v>0.2067966999154076</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5188155781289643</v>
+        <v>0.5188155781289676</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4090702864139197</v>
+        <v>-0.4090702864139195</v>
       </c>
       <c r="G7" t="n">
         <v>1778</v>
@@ -622,16 +610,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9584415886618634</v>
+        <v>0.9584415886618545</v>
       </c>
       <c r="C8" t="n">
-        <v>0.09995054484818255</v>
+        <v>0.09995054484818189</v>
       </c>
       <c r="D8" t="n">
         <v>0.2045951980629741</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4885283026897725</v>
+        <v>0.4885283026897691</v>
       </c>
       <c r="F8" t="n">
         <v>-0.3987645747895679</v>
@@ -647,19 +635,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.908380190890905</v>
+        <v>0.9083801908909042</v>
       </c>
       <c r="C9" t="n">
         <v>0.09592107117380677</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2041331901619282</v>
+        <v>0.2041331901619283</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4698945384516727</v>
+        <v>0.4698945384516724</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4086572209677214</v>
+        <v>-0.4086572209677217</v>
       </c>
       <c r="G9" t="n">
         <v>1778</v>
@@ -672,19 +660,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4059719469622569</v>
+        <v>0.4059719469622534</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04947734822735583</v>
+        <v>0.04947734822735539</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2110945914050937</v>
+        <v>0.2110945914050936</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2343847272354224</v>
+        <v>0.2343847272354205</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4306626935051984</v>
+        <v>-0.4306626935051983</v>
       </c>
       <c r="G10" t="n">
         <v>1778</v>
